--- a/docs/StructureDefinition-BRContatoAssistencial-1.0.xlsx
+++ b/docs/StructureDefinition-BRContatoAssistencial-1.0.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -368,7 +368,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -840,7 +840,7 @@
     <t>The type of encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-type|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -864,7 +864,7 @@
     <t>Broad categorization of the service that is to be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1197,7 +1197,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1275,7 +1275,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1356,7 +1356,7 @@
     <t>Encounter.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1396,7 +1396,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare)
+    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1422,7 +1422,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1672,7 +1672,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment)
+    <t xml:space="preserve">Reference(Appointment|4.0.1)
 </t>
   </si>
   <si>
@@ -1820,7 +1820,7 @@
     <t>Reason why the encounter takes place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1906,7 +1906,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1937,7 +1937,7 @@
     <t>The type of diagnosis this condition represents.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -2182,7 +2182,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.0.1)
 </t>
   </si>
   <si>
@@ -2255,7 +2255,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|Organization)
+    <t xml:space="preserve">Reference(Location|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -2355,7 +2355,7 @@
     <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -2376,7 +2376,7 @@
     <t>Special courtesies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -2397,7 +2397,7 @@
     <t>Special arrangements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -2580,7 +2580,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -3179,7 +3179,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>32</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>192</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>275</v>
       </c>
@@ -8299,7 +8299,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>309</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>323</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>333</v>
       </c>
@@ -9541,7 +9541,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>350</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>357</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>459</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>468</v>
       </c>
@@ -12941,7 +12941,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>474</v>
       </c>
@@ -13285,7 +13285,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>485</v>
       </c>
@@ -14769,7 +14769,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>510</v>
       </c>
@@ -16589,7 +16589,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>540</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>550</v>
       </c>
@@ -17043,7 +17043,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>560</v>
       </c>
@@ -17387,7 +17387,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
         <v>587</v>
       </c>
@@ -18973,7 +18973,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
         <v>625</v>
       </c>
@@ -19429,7 +19429,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
         <v>633</v>
       </c>
@@ -21707,7 +21707,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>674</v>
       </c>
@@ -22163,7 +22163,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="169" hidden="true">
+    <row r="169">
       <c r="A169" t="s" s="2">
         <v>682</v>
       </c>
@@ -22501,7 +22501,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
         <v>686</v>
       </c>
@@ -23409,7 +23409,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180" hidden="true">
+    <row r="180">
       <c r="A180" t="s" s="2">
         <v>703</v>
       </c>
@@ -24199,7 +24199,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
         <v>725</v>
       </c>
@@ -26133,7 +26133,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="204" hidden="true">
+    <row r="204">
       <c r="A204" t="s" s="2">
         <v>776</v>
       </c>
@@ -27503,7 +27503,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="216" hidden="true">
+    <row r="216">
       <c r="A216" t="s" s="2">
         <v>795</v>
       </c>
@@ -27959,7 +27959,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="220" hidden="true">
+    <row r="220">
       <c r="A220" t="s" s="2">
         <v>803</v>
       </c>
@@ -29093,7 +29093,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="230" hidden="true">
+    <row r="230">
       <c r="A230" t="s" s="2">
         <v>832</v>
       </c>
@@ -30801,7 +30801,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="245" hidden="true">
+    <row r="245">
       <c r="A245" t="s" s="2">
         <v>852</v>
       </c>
@@ -31599,12 +31599,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN251">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
